--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487446_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487446_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5327</v>
+        <v>6.6388</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5087</v>
+        <v>4.1227</v>
       </c>
       <c r="F2" t="n">
-        <v>3.024</v>
+        <v>2.5161</v>
       </c>
       <c r="G2" t="n">
         <v>4.4007</v>
@@ -610,13 +610,13 @@
         <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5236</v>
+        <v>0.6297</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7128</v>
+        <v>-0.0988</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2364</v>
+        <v>0.7286</v>
       </c>
       <c r="V2" t="n">
         <v>1.2166</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2949</v>
+        <v>6.168</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7553</v>
+        <v>2.2007</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5396</v>
+        <v>3.9673</v>
       </c>
       <c r="G3" t="n">
         <v>3.5484</v>
@@ -688,13 +688,13 @@
         <v>3.1336</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.333</v>
+        <v>-0.4599</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2358</v>
+        <v>-0.3188</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5688</v>
+        <v>-0.1411</v>
       </c>
       <c r="V3" t="n">
         <v>2.1003</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7924</v>
+        <v>4.6601</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2642</v>
+        <v>2.426</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5282</v>
+        <v>2.2341</v>
       </c>
       <c r="G4" t="n">
         <v>3.3861</v>
@@ -766,13 +766,13 @@
         <v>2.546</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4639</v>
+        <v>0.3316</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5058</v>
+        <v>-0.3441</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9697</v>
+        <v>0.6756</v>
       </c>
       <c r="V4" t="n">
         <v>0.5507</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4634</v>
+        <v>2.744</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4004</v>
+        <v>0.681</v>
       </c>
       <c r="F5" t="n">
         <v>2.063</v>
@@ -844,10 +844,10 @@
         <v>2.3502</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1157</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9504</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="U5" t="n">
         <v>-0.1653</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.344</v>
+        <v>2.6616</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.148</v>
+        <v>-0.8839</v>
       </c>
       <c r="F6" t="n">
-        <v>3.492</v>
+        <v>3.5455</v>
       </c>
       <c r="G6" t="n">
         <v>0.9157999999999999</v>
@@ -922,13 +922,13 @@
         <v>2.546</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6466</v>
+        <v>-0.3291</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8316</v>
+        <v>-0.5676</v>
       </c>
       <c r="U6" t="n">
-        <v>0.185</v>
+        <v>0.2385</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2754</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. IGLESIAS FERNANDEZ</t>
+          <t>S. MARTINEZ GRANDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3495</v>
+        <v>0.3314</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8912</v>
+        <v>-0.792</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2407</v>
+        <v>1.1234</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0984</v>
+        <v>1.6072</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0483</v>
+        <v>0.2631</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0501</v>
+        <v>1.3441</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4172</v>
+        <v>1.5208</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0649</v>
+        <v>1.5515</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3522</v>
+        <v>-0.0308</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3188</v>
+        <v>0.0864</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0166</v>
+        <v>-1.2884</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6978</v>
+        <v>1.3749</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.9585</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.917</v>
+        <v>-3.1336</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9585</v>
+        <v>2.546</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8755</v>
+        <v>-0.6883</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2745</v>
+        <v>-0.3958</v>
       </c>
       <c r="U7" t="n">
-        <v>0.601</v>
+        <v>-0.2924</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6659</v>
+        <v>1.2166</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. GERPE FUENTES</t>
+          <t>A. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7499</v>
+        <v>-0.6992</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7416</v>
+        <v>-2.7528</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0083</v>
+        <v>2.0536</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8864</v>
+        <v>1.0984</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2042</v>
+        <v>0.0483</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6822</v>
+        <v>1.0501</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6822</v>
+        <v>1.4172</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.0649</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6822</v>
+        <v>0.3522</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2042</v>
+        <v>-0.3188</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2042</v>
+        <v>-1.0166</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.6978</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1958</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.917</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1958</v>
+        <v>1.9585</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0594</v>
+        <v>0.8268</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0594</v>
+        <v>0.4129</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.4139</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. MARTINEZ GRANDA</t>
+          <t>N. GERPE FUENTES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8559</v>
+        <v>-0.7499</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5248</v>
+        <v>-0.7416</v>
       </c>
       <c r="F9" t="n">
-        <v>0.669</v>
+        <v>-0.0083</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6072</v>
+        <v>-0.8864</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2631</v>
+        <v>-0.2042</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3441</v>
+        <v>-0.6822</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5208</v>
+        <v>-0.6822</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5515</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0308</v>
+        <v>-0.6822</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0864</v>
+        <v>-0.2042</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2884</v>
+        <v>-0.2042</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3749</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1336</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.546</v>
+        <v>0.1958</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8755</v>
+        <v>-0.0594</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1286</v>
+        <v>-0.0594</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7469</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8692</v>
+        <v>-0.8365</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3515</v>
+        <v>0.4109</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2207</v>
+        <v>-1.2474</v>
       </c>
       <c r="G10" t="n">
         <v>0.0329</v>
@@ -1234,13 +1234,13 @@
         <v>0.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0772</v>
+        <v>-0.0446</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3564</v>
+        <v>-0.297</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2792</v>
+        <v>0.2525</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2166</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5608</v>
+        <v>-1.2862</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6694</v>
+        <v>-1.4483</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1087</v>
+        <v>0.1621</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2004</v>
@@ -1312,13 +1312,13 @@
         <v>1.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7301</v>
+        <v>-0.4555</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4158</v>
+        <v>-0.1947</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3143</v>
+        <v>-0.2608</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8260999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9311</v>
+        <v>-1.8449</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9198</v>
+        <v>-0.8604000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0112</v>
+        <v>-0.9845</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6135</v>
@@ -1390,13 +1390,13 @@
         <v>0.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4927</v>
+        <v>-0.4065</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2376</v>
+        <v>-0.1782</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2551</v>
+        <v>-0.2283</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2166</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0221</v>
+        <v>-2.108</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5059</v>
+        <v>-1.5918</v>
       </c>
       <c r="F13" t="n">
         <v>-0.5162</v>
@@ -1468,10 +1468,10 @@
         <v>0.7834</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3323</v>
+        <v>0.2464</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1476</v>
+        <v>0.0618</v>
       </c>
       <c r="U13" t="n">
         <v>0.1847</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.7879</v>
+        <v>15.6792</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1206000000000005</v>
+        <v>0.7704999999999984</v>
       </c>
       <c r="F14" t="n">
-        <v>14.9088</v>
+        <v>14.9087</v>
       </c>
       <c r="G14" t="n">
         <v>12.2178</v>
@@ -1546,13 +1546,13 @@
         <v>19.5848</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.1349</v>
+        <v>-1.244</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.540499999999999</v>
+        <v>-2.6496</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4056</v>
+        <v>1.4059</v>
       </c>
       <c r="V14" t="n">
         <v>1.7673</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4277</v>
+        <v>2.9791</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0776</v>
+        <v>1.8962</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3502</v>
+        <v>1.0829</v>
       </c>
       <c r="G15" t="n">
         <v>0.3987</v>
@@ -1624,13 +1624,13 @@
         <v>2.9377</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5217000000000001</v>
+        <v>0.0297</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3486</v>
+        <v>-0.5299</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8269</v>
+        <v>0.5596</v>
       </c>
       <c r="V15" t="n">
         <v>1.7673</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>M. IGLESIAS VALDERRAMA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.698</v>
+        <v>0.4336</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0601</v>
+        <v>-0.078</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3621</v>
+        <v>0.5115</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8779</v>
+        <v>0.1783</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4681</v>
+        <v>-0.0946</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4097</v>
+        <v>0.2729</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1497</v>
+        <v>0.0408</v>
       </c>
       <c r="K16" t="n">
-        <v>4.0284</v>
+        <v>0.0408</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1212</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2718</v>
+        <v>0.1375</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5603</v>
+        <v>-0.1354</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2885</v>
+        <v>0.2729</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.546</v>
+        <v>0.1958</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.0921</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.546</v>
+        <v>0.1958</v>
       </c>
       <c r="S16" t="n">
-        <v>3.524</v>
+        <v>0.0594</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7272</v>
+        <v>-0.1188</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.1782</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.1578</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. IGLESIAS VALDERRAMA</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3266</v>
+        <v>-0.6381</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.078</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4046</v>
+        <v>-0.5492</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1783</v>
+        <v>2.8779</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0946</v>
+        <v>2.4681</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2729</v>
+        <v>0.4097</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0408</v>
+        <v>4.1497</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0408</v>
+        <v>4.0284</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.1212</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1375</v>
+        <v>-1.2718</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1354</v>
+        <v>-1.5603</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2729</v>
+        <v>0.2885</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1958</v>
+        <v>-2.546</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-5.0921</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1958</v>
+        <v>2.546</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0475</v>
+        <v>1.1879</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1188</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0713</v>
+        <v>0.6098</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-2.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1315</v>
+        <v>-0.7931</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1742</v>
+        <v>0.0304</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.8236</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7252</v>
@@ -1858,13 +1858,13 @@
         <v>2.7419</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3267</v>
+        <v>0.0116</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8028</v>
+        <v>-0.5981</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4761</v>
+        <v>0.6098</v>
       </c>
       <c r="V18" t="n">
         <v>0.3329</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SANJURJO BOTEJARA</t>
+          <t>F. VIDAL PATIÑO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1882</v>
+        <v>-0.8023</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2633</v>
+        <v>-2.669</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9249000000000001</v>
+        <v>1.8666</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3278</v>
+        <v>-2.8942</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3634</v>
+        <v>-3.0106</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0356</v>
+        <v>0.1164</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6038</v>
+        <v>-1.9598</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2457</v>
+        <v>-1.9242</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6418</v>
+        <v>-0.0356</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.276</v>
+        <v>-0.9344</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8822</v>
+        <v>-1.0864</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3938</v>
+        <v>0.152</v>
       </c>
       <c r="P19" t="n">
+        <v>0.9792</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.9792</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.9585</v>
-      </c>
       <c r="R19" t="n">
-        <v>0.9792</v>
+        <v>1.9585</v>
       </c>
       <c r="S19" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.4467</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.517</v>
+        <v>-0.0053</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5884</v>
+        <v>0.452</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6083</v>
+        <v>0.6659</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6083</v>
+        <v>0.2754</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2166</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. VIDAL PATIÑO</t>
+          <t>P. SANJURJO BOTEJARA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2606</v>
+        <v>-1.0149</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1807</v>
+        <v>0.0437</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9201</v>
+        <v>-1.0586</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.8942</v>
+        <v>0.3278</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.0106</v>
+        <v>1.3634</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1164</v>
+        <v>-1.0356</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9598</v>
+        <v>1.6038</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.9242</v>
+        <v>2.2457</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0356</v>
+        <v>-0.6418</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9344</v>
+        <v>-1.276</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0864</v>
+        <v>-0.8822</v>
       </c>
       <c r="O20" t="n">
-        <v>0.152</v>
+        <v>-0.3938</v>
       </c>
       <c r="P20" t="n">
+        <v>-0.9792</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1.9585</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.9792</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-0.9792</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.9585</v>
-      </c>
       <c r="S20" t="n">
-        <v>-0.0115</v>
+        <v>0.2448</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.517</v>
+        <v>-0.21</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5054</v>
+        <v>0.4548</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6659</v>
+        <v>-0.6083</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2754</v>
+        <v>0.6083</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3905</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7093</v>
+        <v>-2.2966</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0512</v>
+        <v>-1.6652</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6581</v>
+        <v>-0.6313</v>
       </c>
       <c r="G21" t="n">
         <v>0.7685</v>
@@ -2092,13 +2092,13 @@
         <v>1.3709</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3436</v>
+        <v>-0.2436</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3546</v>
+        <v>-0.2594</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.011</v>
+        <v>0.0157</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2754</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5359</v>
+        <v>-2.4778</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5992</v>
+        <v>-1.7016</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9367</v>
+        <v>-0.7763</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3427</v>
@@ -2170,13 +2170,13 @@
         <v>0.5875</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4151</v>
+        <v>0.4732</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.4193</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1066</v>
+        <v>0.0538</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6691</v>
+        <v>-3.9971</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.999</v>
+        <v>-5.4873</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3299</v>
+        <v>1.4903</v>
       </c>
       <c r="G23" t="n">
         <v>-3.8714</v>
@@ -2248,13 +2248,13 @@
         <v>1.9585</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3265</v>
+        <v>0.3455</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5764</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2498</v>
+        <v>0.4102</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2754</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.7459</v>
+        <v>-6.1808</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.7009</v>
+        <v>-5.1892</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.045</v>
+        <v>-0.9916</v>
       </c>
       <c r="G24" t="n">
         <v>-4.9356</v>
@@ -2326,13 +2326,13 @@
         <v>1.3709</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-0.4202</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1286</v>
+        <v>-0.617</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1433</v>
+        <v>0.1967</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2166</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.7882</v>
+        <v>-14.788</v>
       </c>
       <c r="E25" t="n">
-        <v>-14.9088</v>
+        <v>-14.9089</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1208</v>
+        <v>0.1206999999999998</v>
       </c>
       <c r="G25" t="n">
         <v>-12.2179</v>
@@ -2404,13 +2404,13 @@
         <v>16.6469</v>
       </c>
       <c r="S25" t="n">
-        <v>2.134899999999999</v>
+        <v>2.135</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.4057</v>
+        <v>-1.4058</v>
       </c>
       <c r="U25" t="n">
-        <v>3.5405</v>
+        <v>3.5406</v>
       </c>
       <c r="V25" t="n">
         <v>-1.7674</v>
